--- a/Output/post_x_combined_key_coefficients.xlsx
+++ b/Output/post_x_combined_key_coefficients.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">0.008 (0.011)</t>
+    <t xml:space="preserve">0.010 (0.011)</t>
   </si>
   <si>
     <t xml:space="preserve">+</t>
@@ -44,82 +44,85 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">0.005 (0.012)</t>
+    <t xml:space="preserve">0.005 (0.011)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_mean_educ</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002 (0.013)</t>
+    <t xml:space="preserve">0.003 (0.012)</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve">0.002 (0.012)</t>
+  </si>
+  <si>
     <t xml:space="preserve">mun_pre_all_mean_izq_der</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.050*** (0.016)</t>
+    <t xml:space="preserve">-0.054*** (0.016)</t>
   </si>
   <si>
     <t xml:space="preserve">-***</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.054*** (0.016)</t>
+    <t xml:space="preserve">-0.055*** (0.016)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_desempleado</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582 (0.413)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.543 (0.410)</t>
+    <t xml:space="preserve">0.529 (0.403)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.494 (0.407)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_en_pareja</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.012 (0.186)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.034 (0.179)</t>
+    <t xml:space="preserve">-0.038 (0.181)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.044 (0.177)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_hombre</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132 (1.038)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.271 (1.084)</t>
+    <t xml:space="preserve">0.097 (1.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.270 (1.054)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_interes_pol_mucho</t>
   </si>
   <si>
-    <t xml:space="preserve">0.314 (0.195)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.265 (0.193)</t>
+    <t xml:space="preserve">0.325* (0.192)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.272 (0.191)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_rural</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.040 (0.047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.037 (0.047)</t>
+    <t xml:space="preserve">-0.047 (0.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.044 (0.046)</t>
   </si>
   <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.093 (0.237)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.084 (0.244)</t>
+    <t xml:space="preserve">-0.124 (0.248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.099 (0.249)</t>
   </si>
 </sst>
 </file>
@@ -524,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -535,16 +538,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>7467</v>
@@ -552,16 +555,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
       </c>
       <c r="E7" t="n">
         <v>7412</v>
@@ -569,13 +572,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -586,13 +589,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -603,13 +606,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
@@ -620,13 +623,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -637,13 +640,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
@@ -654,13 +657,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
@@ -671,13 +674,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
         <v>8</v>
@@ -688,13 +691,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -705,13 +708,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>13</v>
@@ -722,13 +725,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -739,13 +742,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -756,13 +759,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>

--- a/Output/post_x_combined_key_coefficients.xlsx
+++ b/Output/post_x_combined_key_coefficients.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -107,15 +107,6 @@
     <t xml:space="preserve">0.272 (0.191)</t>
   </si>
   <si>
-    <t xml:space="preserve">mun_pre_all_share_rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.047 (0.045)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.044 (0.046)</t>
-  </si>
-  <si>
     <t xml:space="preserve">mun_pre_all_share_voto_blanco_nulo</t>
   </si>
   <si>
@@ -123,6 +114,12 @@
   </si>
   <si>
     <t xml:space="preserve">-0.099 (0.249)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">popdensgeo2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 (0.004)</t>
   </si>
 </sst>
 </file>
@@ -754,7 +751,7 @@
         <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>7467</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="19">
@@ -765,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
   </sheetData>
